--- a/MAJSushiConfig/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-composition-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-composition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -480,7 +480,7 @@
     <t>canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-composition-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
     <t>Composition.meta.security</t>
@@ -861,7 +861,7 @@
     <t>Composition.extension:data-enterer.extension:party.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0)
 </t>
   </si>
   <si>
@@ -990,7 +990,7 @@
     <t>Composition.extension:informant.extension:party.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-related-person-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-related-person-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1049,7 +1049,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-doc-vs-participation-type|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-doc-vs-participation-type|0.1.0</t>
   </si>
   <si>
     <t>Composition.extension:information-recipient.extension:function</t>
@@ -1152,7 +1152,7 @@
     <t>Composition.extension:participant.extension:type.value[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-doc-vs-participation-type-participant|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-doc-vs-participation-type-participant|0.1.0</t>
   </si>
   <si>
     <t>Composition.extension:participant.extension:function</t>
@@ -1515,7 +1515,7 @@
     <t>Composition.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1629,7 +1629,7 @@
     <t>Composition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-encounter-care-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-encounter-care-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1694,7 +1694,7 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-device-auteur-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-device-auteur-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1731,7 +1731,7 @@
     <t>Composition.author.extension:time</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-author-time-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-author-time-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -1986,7 +1986,7 @@
     <t>Composition.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-organization-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0)
 </t>
   </si>
   <si>
@@ -2079,7 +2079,7 @@
   </si>
   <si>
     <t>Identifier
-Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-composition-document|0.1.0)</t>
+Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0)</t>
   </si>
   <si>
     <t>Target of the relationship</t>
@@ -2450,7 +2450,7 @@
     <t>performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-performer-event-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-performer-event-extension|0.1.0}
 </t>
   </si>
   <si>
